--- a/dataland-framework-toolbox/inputs/lksg/lksg.xlsx
+++ b/dataland-framework-toolbox/inputs/lksg/lksg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d92928\Documents\Projects\Dataland\Dataland\dataland-framework-toolbox\inputs\lksg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71747903-6636-40AB-9D1A-9E8FBEDDCDA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643C8AA5-520F-464A-838C-846213FAC209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{64EA21DF-A91B-4C8A-A36C-EACA4F178F40}"/>
   </bookViews>
@@ -1630,13 +1630,13 @@
     <t>AmountWithCurrencyComponent</t>
   </si>
   <si>
-    <t>LkSG Risk Positions</t>
-  </si>
-  <si>
-    <t>LkSG General Violations</t>
-  </si>
-  <si>
     <t>LkSG Grievance Mechanism Assessment</t>
+  </si>
+  <si>
+    <t>LkSG Risk Position Assessments</t>
+  </si>
+  <si>
+    <t>LkSG General Violations Assessments</t>
   </si>
 </sst>
 </file>
@@ -2816,7 +2816,7 @@
         <v>271</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H27" s="9"/>
       <c r="K27" s="7" t="s">
@@ -3054,7 +3054,7 @@
         <v>280</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H36" s="9"/>
       <c r="K36" s="7" t="s">
@@ -3527,7 +3527,7 @@
         <v>300</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H56" s="9"/>
       <c r="K56" s="7" t="s">

--- a/dataland-framework-toolbox/inputs/lksg/lksg.xlsx
+++ b/dataland-framework-toolbox/inputs/lksg/lksg.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d92928\Documents\Projects\Dataland\Dataland\dataland-framework-toolbox\inputs\lksg\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dataland\Dataland\dataland-framework-toolbox\inputs\lksg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643C8AA5-520F-464A-838C-846213FAC209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3E13DA-8A87-4B99-A77F-B604E67B1D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{64EA21DF-A91B-4C8A-A36C-EACA4F178F40}"/>
+    <workbookView xWindow="-4170" yWindow="-21720" windowWidth="38640" windowHeight="21240" xr2:uid="{64EA21DF-A91B-4C8A-A36C-EACA4F178F40}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="522">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -1624,9 +1624,6 @@
     <t>ISO2 Codes Multi-Select Dropdown</t>
   </si>
   <si>
-    <t>119</t>
-  </si>
-  <si>
     <t>AmountWithCurrencyComponent</t>
   </si>
   <si>
@@ -1637,6 +1634,9 @@
   </si>
   <si>
     <t>LkSG General Violations Assessments</t>
+  </si>
+  <si>
+    <t>120</t>
   </si>
 </sst>
 </file>
@@ -2129,25 +2129,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBCA27A-793A-4293-9394-36A2BE726731}">
   <dimension ref="A1:M199"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.33203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="78.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="150.88671875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="87.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="39.6640625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="23.109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="24.88671875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="18.44140625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.36328125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="78.453125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="150.90625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="87.36328125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="39.6328125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="23.08984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="24.90625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="18.453125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="4"/>
+    <col min="14" max="16384" width="9.08984375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -2389,10 +2389,10 @@
         <v>255</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2409,10 +2409,10 @@
         <v>256</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>271</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H27" s="9"/>
       <c r="K27" s="7" t="s">
@@ -2826,7 +2826,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>29</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>30</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
         <v>31</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>32</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>33</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>34</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="4">
         <v>35</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
         <v>36</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>37</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>280</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H36" s="9"/>
       <c r="K36" s="7" t="s">
@@ -3064,7 +3064,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
         <v>38</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="4">
         <v>39</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>40</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>41</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>42</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>43</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>44</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="4">
         <v>45</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="4">
         <v>46</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="4">
         <v>47</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
         <v>48</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
         <v>49</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>50</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
         <v>51</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
         <v>52</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="4">
         <v>53</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
         <v>54</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="4">
         <v>55</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="4">
         <v>56</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="4">
         <v>57</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>300</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H56" s="9"/>
       <c r="K56" s="7" t="s">
@@ -3537,7 +3537,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="4">
         <v>60</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="4">
         <v>61</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="4">
         <v>62</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="4">
         <v>63</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
         <v>64</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="4">
         <v>65</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="4">
         <v>66</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="4">
         <v>67</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>68</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="4">
         <v>69</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4">
         <v>70</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="4">
         <v>71</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="4">
         <v>72</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="4">
         <v>73</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="4">
         <v>74</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="4">
         <v>75</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="4">
         <v>76</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="4">
         <v>77</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="4">
         <v>78</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="4">
         <v>79</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="4">
         <v>80</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="4">
         <v>81</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="4">
         <v>82</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="4">
         <v>83</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="4">
         <v>84</v>
       </c>
@@ -4154,7 +4154,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="4">
         <v>85</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
         <v>86</v>
       </c>
@@ -4206,7 +4206,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="4">
         <v>87</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="4">
         <v>88</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="4">
         <v>89</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="4">
         <v>90</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="4">
         <v>91</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="4">
         <v>92</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="4">
         <v>93</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="4">
         <v>94</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="4">
         <v>95</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="4">
         <v>96</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="4">
         <v>97</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="4">
         <v>98</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="4">
         <v>99</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="4">
         <v>100</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="4">
         <v>101</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="4">
         <v>102</v>
       </c>
@@ -4616,7 +4616,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="4">
         <v>103</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="4">
         <v>104</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="4">
         <v>105</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" s="4">
         <v>106</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" s="4">
         <v>107</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" s="4">
         <v>108</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="4">
         <v>109</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="4">
         <v>110</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="4">
         <v>111</v>
       </c>
@@ -4844,7 +4844,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="4">
         <v>112</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" s="4">
         <v>113</v>
       </c>
@@ -4890,7 +4890,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" s="4">
         <v>114</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" s="4">
         <v>115</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" s="4">
         <v>116</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="4">
         <v>117</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="4">
         <v>118</v>
       </c>
@@ -5029,7 +5029,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="4">
         <v>119</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="4">
         <v>120</v>
       </c>
@@ -5068,14 +5068,12 @@
       <c r="G117" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K117" s="7" t="s">
-        <v>517</v>
-      </c>
+      <c r="K117" s="7"/>
       <c r="L117" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="4">
         <v>121</v>
       </c>
@@ -5095,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L118" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="4">
         <v>122</v>
       </c>
@@ -5121,13 +5119,13 @@
         <v>20</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L119" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="4">
         <v>123</v>
       </c>
@@ -5150,13 +5148,13 @@
         <v>22</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L120" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="4">
         <v>124</v>
       </c>
@@ -5176,13 +5174,13 @@
         <v>20</v>
       </c>
       <c r="K121" s="7" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L121" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" s="4">
         <v>125</v>
       </c>
@@ -5205,13 +5203,13 @@
         <v>22</v>
       </c>
       <c r="K122" s="7" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L122" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="4">
         <v>126</v>
       </c>
@@ -5234,13 +5232,13 @@
         <v>22</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L123" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="4">
         <v>127</v>
       </c>
@@ -5266,7 +5264,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="4">
         <v>128</v>
       </c>
@@ -5286,7 +5284,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" s="4">
         <v>129</v>
       </c>
@@ -5312,7 +5310,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" s="4">
         <v>130</v>
       </c>
@@ -5338,7 +5336,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" s="4">
         <v>131</v>
       </c>
@@ -5364,7 +5362,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" s="4">
         <v>132</v>
       </c>
@@ -5390,7 +5388,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" s="4">
         <v>133</v>
       </c>
@@ -5416,7 +5414,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" s="4">
         <v>134</v>
       </c>
@@ -5445,7 +5443,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" s="4">
         <v>135</v>
       </c>
@@ -5474,7 +5472,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" s="4">
         <v>136</v>
       </c>
@@ -5494,7 +5492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" s="4">
         <v>137</v>
       </c>
@@ -5520,7 +5518,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" s="4">
         <v>138</v>
       </c>
@@ -5546,7 +5544,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" s="4">
         <v>139</v>
       </c>
@@ -5575,7 +5573,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" s="4">
         <v>140</v>
       </c>
@@ -5604,7 +5602,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" s="4">
         <v>141</v>
       </c>
@@ -5624,7 +5622,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" s="4">
         <v>142</v>
       </c>
@@ -5650,7 +5648,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" s="4">
         <v>143</v>
       </c>
@@ -5679,7 +5677,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" s="4">
         <v>144</v>
       </c>
@@ -5708,7 +5706,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" s="4">
         <v>145</v>
       </c>
@@ -5728,7 +5726,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" s="4">
         <v>146</v>
       </c>
@@ -5754,7 +5752,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" s="4">
         <v>147</v>
       </c>
@@ -5783,7 +5781,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A145" s="4">
         <v>148</v>
       </c>
@@ -5812,7 +5810,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A146" s="4">
         <v>149</v>
       </c>
@@ -5832,7 +5830,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A147" s="4">
         <v>150</v>
       </c>
@@ -5858,7 +5856,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A148" s="4">
         <v>151</v>
       </c>
@@ -5884,7 +5882,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149" s="4">
         <v>152</v>
       </c>
@@ -5913,7 +5911,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A150" s="4">
         <v>153</v>
       </c>
@@ -5942,7 +5940,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A151" s="4">
         <v>154</v>
       </c>
@@ -5968,7 +5966,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A152" s="4">
         <v>155</v>
       </c>
@@ -5991,7 +5989,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A153" s="4">
         <v>156</v>
       </c>
@@ -6017,7 +6015,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A154" s="4">
         <v>157</v>
       </c>
@@ -6037,7 +6035,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A155" s="4">
         <v>158</v>
       </c>
@@ -6063,7 +6061,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A156" s="4">
         <v>159</v>
       </c>
@@ -6083,7 +6081,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A157" s="4">
         <v>160</v>
       </c>
@@ -6112,7 +6110,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A158" s="4">
         <v>161</v>
       </c>
@@ -6138,7 +6136,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A159" s="4">
         <v>162</v>
       </c>
@@ -6167,7 +6165,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A160" s="4">
         <v>163</v>
       </c>
@@ -6196,7 +6194,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A161" s="4">
         <v>164</v>
       </c>
@@ -6222,7 +6220,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A162" s="4">
         <v>165</v>
       </c>
@@ -6242,7 +6240,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A163" s="4">
         <v>166</v>
       </c>
@@ -6262,7 +6260,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A164" s="4">
         <v>167</v>
       </c>
@@ -6288,7 +6286,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A165" s="4">
         <v>168</v>
       </c>
@@ -6317,7 +6315,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A166" s="4">
         <v>169</v>
       </c>
@@ -6346,7 +6344,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A167" s="4">
         <v>170</v>
       </c>
@@ -6372,7 +6370,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A168" s="4">
         <v>171</v>
       </c>
@@ -6401,7 +6399,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A169" s="4">
         <v>172</v>
       </c>
@@ -6430,7 +6428,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A170" s="4">
         <v>173</v>
       </c>
@@ -6456,7 +6454,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" s="4">
         <v>174</v>
       </c>
@@ -6476,7 +6474,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A172" s="4">
         <v>175</v>
       </c>
@@ -6502,7 +6500,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A173" s="4">
         <v>176</v>
       </c>
@@ -6528,7 +6526,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A174" s="4">
         <v>177</v>
       </c>
@@ -6554,7 +6552,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A175" s="4">
         <v>178</v>
       </c>
@@ -6580,7 +6578,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A176" s="4">
         <v>179</v>
       </c>
@@ -6606,7 +6604,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A177" s="4">
         <v>180</v>
       </c>
@@ -6632,7 +6630,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A178" s="4">
         <v>181</v>
       </c>
@@ -6661,7 +6659,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A179" s="4">
         <v>182</v>
       </c>
@@ -6690,7 +6688,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A180" s="4">
         <v>183</v>
       </c>
@@ -6716,7 +6714,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A181" s="4">
         <v>184</v>
       </c>
@@ -6736,7 +6734,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A182" s="4">
         <v>185</v>
       </c>
@@ -6762,7 +6760,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A183" s="4">
         <v>186</v>
       </c>
@@ -6788,7 +6786,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A184" s="4">
         <v>187</v>
       </c>
@@ -6814,7 +6812,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A185" s="4">
         <v>188</v>
       </c>
@@ -6840,7 +6838,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A186" s="4">
         <v>189</v>
       </c>
@@ -6866,7 +6864,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A187" s="4">
         <v>190</v>
       </c>
@@ -6895,7 +6893,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A188" s="4">
         <v>191</v>
       </c>
@@ -6921,7 +6919,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A189" s="4">
         <v>192</v>
       </c>
@@ -6941,7 +6939,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A190" s="4">
         <v>193</v>
       </c>
@@ -6967,7 +6965,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A191" s="4">
         <v>194</v>
       </c>
@@ -6993,7 +6991,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A192" s="4">
         <v>195</v>
       </c>
@@ -7019,7 +7017,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A193" s="4">
         <v>196</v>
       </c>
@@ -7045,7 +7043,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A194" s="4">
         <v>197</v>
       </c>
@@ -7074,7 +7072,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A195" s="4">
         <v>198</v>
       </c>
@@ -7100,7 +7098,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A196" s="4">
         <v>199</v>
       </c>
@@ -7120,7 +7118,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A197" s="4">
         <v>200</v>
       </c>
@@ -7146,7 +7144,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A198" s="4">
         <v>201</v>
       </c>
@@ -7175,7 +7173,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A199" s="9">
         <v>202</v>
       </c>
@@ -7210,15 +7208,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5B0D63-9F6C-44CA-87BF-274BCE12F441}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="57" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>460</v>
       </c>
@@ -7232,7 +7230,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>464</v>
       </c>
@@ -7246,7 +7244,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>467</v>
       </c>
@@ -7260,7 +7258,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>471</v>
       </c>
@@ -7274,7 +7272,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>475</v>
       </c>
@@ -7288,7 +7286,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>478</v>
       </c>
@@ -7302,7 +7300,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>481</v>
       </c>
@@ -7316,7 +7314,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>459</v>
       </c>
@@ -7330,7 +7328,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>486</v>
       </c>
@@ -7344,7 +7342,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>489</v>
       </c>
@@ -7358,7 +7356,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>492</v>
       </c>
@@ -7372,7 +7370,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>495</v>
       </c>
@@ -7386,7 +7384,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>498</v>
       </c>
@@ -7400,7 +7398,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>44</v>
       </c>

--- a/dataland-framework-toolbox/inputs/lksg/lksg.xlsx
+++ b/dataland-framework-toolbox/inputs/lksg/lksg.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dataland\Dataland\dataland-framework-toolbox\inputs\lksg\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d92928\Documents\Projects\Dataland\Dataland\dataland-framework-toolbox\inputs\lksg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3E13DA-8A87-4B99-A77F-B604E67B1D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957C0BE4-2217-47B2-B0A9-C5B44146C45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4170" yWindow="-21720" windowWidth="38640" windowHeight="21240" xr2:uid="{64EA21DF-A91B-4C8A-A36C-EACA4F178F40}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{64EA21DF-A91B-4C8A-A36C-EACA4F178F40}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="522">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -1791,11 +1791,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
@@ -1813,6 +1808,11 @@
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2129,25 +2129,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBCA27A-793A-4293-9394-36A2BE726731}">
   <dimension ref="A1:M199"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.36328125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="78.453125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="150.90625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="87.36328125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="39.6328125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="23.08984375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="24.90625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="18.453125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="78.44140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="150.88671875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="87.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="39.6640625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="23.109375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="24.88671875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="18.44140625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.08984375" style="4"/>
+    <col min="14" max="16384" width="9.109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2178,7 +2178,7 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -2188,7 +2188,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -2204,14 +2204,14 @@
       <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="6" t="s">
         <v>16</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2270,14 +2270,15 @@
       <c r="G5" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="14">
+        <f>A4</f>
         <v>3</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -2293,11 +2294,11 @@
       <c r="E6" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="6" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2316,14 +2317,14 @@
       <c r="G7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="12" t="s">
         <v>505</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -2343,7 +2344,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2359,20 +2360,20 @@
       <c r="E9" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="14" t="s">
         <v>459</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -2392,7 +2393,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2412,7 +2413,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2432,7 +2433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2451,14 +2452,14 @@
       <c r="G13" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="14">
         <v>11</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -2477,14 +2478,14 @@
       <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="14">
         <v>11</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2500,17 +2501,17 @@
       <c r="E15" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="K15" s="15" t="s">
         <v>44</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -2526,17 +2527,17 @@
       <c r="E16" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="K16" s="15" t="s">
         <v>44</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2555,14 +2556,14 @@
       <c r="G17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="14">
         <v>11</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -2581,14 +2582,14 @@
       <c r="G18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K18" s="7" t="s">
+      <c r="K18" s="15" t="s">
         <v>458</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -2604,17 +2605,17 @@
       <c r="E19" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="K19" s="7" t="s">
+      <c r="K19" s="15" t="s">
         <v>458</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -2630,20 +2631,20 @@
       <c r="E20" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="6" t="s">
         <v>17</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="15">
         <v>11</v>
       </c>
       <c r="L20" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -2659,20 +2660,20 @@
       <c r="E21" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="6" t="s">
         <v>446</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K21" s="15">
         <v>11</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -2688,17 +2689,17 @@
       <c r="E22" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="15">
         <v>11</v>
       </c>
       <c r="L22" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -2714,17 +2715,17 @@
       <c r="E23" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K23" s="15">
         <v>11</v>
       </c>
       <c r="L23" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -2743,11 +2744,11 @@
       <c r="G24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="J24" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -2766,14 +2767,14 @@
       <c r="G25" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K25" s="7">
+      <c r="K25" s="15">
         <v>23</v>
       </c>
       <c r="L25" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -2792,14 +2793,14 @@
       <c r="G26" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K26" s="7" t="s">
+      <c r="K26" s="15" t="s">
         <v>443</v>
       </c>
       <c r="L26" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -2818,15 +2819,15 @@
       <c r="G27" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="H27" s="9"/>
-      <c r="K27" s="7" t="s">
+      <c r="H27" s="6"/>
+      <c r="K27" s="15" t="s">
         <v>457</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>29</v>
       </c>
@@ -2845,14 +2846,14 @@
       <c r="G28" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="15">
         <v>23</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>30</v>
       </c>
@@ -2871,11 +2872,11 @@
       <c r="G29" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>31</v>
       </c>
@@ -2894,14 +2895,14 @@
       <c r="G30" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="15">
         <v>30</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>32</v>
       </c>
@@ -2920,14 +2921,14 @@
       <c r="G31" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="15">
         <v>30</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>33</v>
       </c>
@@ -2946,14 +2947,14 @@
       <c r="G32" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K32" s="15">
         <v>30</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>34</v>
       </c>
@@ -2972,14 +2973,14 @@
       <c r="G33" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K33" s="15">
         <v>30</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>35</v>
       </c>
@@ -2998,14 +2999,14 @@
       <c r="G34" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="15">
         <v>30</v>
       </c>
       <c r="L34" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>36</v>
       </c>
@@ -3024,20 +3025,20 @@
       <c r="G35" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H35" s="15" t="s">
+      <c r="H35" s="12" t="s">
         <v>505</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="7" t="s">
+      <c r="K35" s="15" t="s">
         <v>45</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>37</v>
       </c>
@@ -3056,15 +3057,15 @@
       <c r="G36" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="H36" s="9"/>
-      <c r="K36" s="7" t="s">
+      <c r="H36" s="6"/>
+      <c r="K36" s="15" t="s">
         <v>45</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>38</v>
       </c>
@@ -3083,14 +3084,14 @@
       <c r="G37" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K37" s="7" t="s">
+      <c r="K37" s="15" t="s">
         <v>45</v>
       </c>
       <c r="L37" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>39</v>
       </c>
@@ -3109,14 +3110,14 @@
       <c r="G38" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K38" s="7" t="s">
+      <c r="K38" s="15" t="s">
         <v>45</v>
       </c>
       <c r="L38" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>40</v>
       </c>
@@ -3135,14 +3136,14 @@
       <c r="G39" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K39" s="7" t="s">
+      <c r="K39" s="15" t="s">
         <v>46</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>41</v>
       </c>
@@ -3161,14 +3162,14 @@
       <c r="G40" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K40" s="7">
+      <c r="K40" s="15">
         <v>30</v>
       </c>
       <c r="L40" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>42</v>
       </c>
@@ -3187,14 +3188,14 @@
       <c r="G41" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K41" s="7">
+      <c r="K41" s="15">
         <v>30</v>
       </c>
       <c r="L41" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>43</v>
       </c>
@@ -3213,14 +3214,14 @@
       <c r="G42" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K42" s="7">
+      <c r="K42" s="15">
         <v>30</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>44</v>
       </c>
@@ -3239,11 +3240,11 @@
       <c r="G43" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J43" s="9" t="s">
+      <c r="J43" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>45</v>
       </c>
@@ -3262,11 +3263,11 @@
       <c r="G44" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J44" s="9" t="s">
+      <c r="J44" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>46</v>
       </c>
@@ -3285,14 +3286,14 @@
       <c r="G45" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K45" s="7" t="s">
+      <c r="K45" s="15" t="s">
         <v>47</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>47</v>
       </c>
@@ -3311,11 +3312,11 @@
       <c r="G46" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J46" s="9" t="s">
+      <c r="J46" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>48</v>
       </c>
@@ -3334,11 +3335,11 @@
       <c r="G47" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J47" s="9" t="s">
+      <c r="J47" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>49</v>
       </c>
@@ -3357,14 +3358,14 @@
       <c r="G48" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K48" s="7" t="s">
+      <c r="K48" s="15" t="s">
         <v>48</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>50</v>
       </c>
@@ -3383,11 +3384,11 @@
       <c r="G49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J49" s="9" t="s">
+      <c r="J49" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>51</v>
       </c>
@@ -3406,11 +3407,11 @@
       <c r="G50" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J50" s="9" t="s">
+      <c r="J50" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>52</v>
       </c>
@@ -3430,7 +3431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>53</v>
       </c>
@@ -3450,7 +3451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>54</v>
       </c>
@@ -3470,7 +3471,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>55</v>
       </c>
@@ -3490,7 +3491,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>56</v>
       </c>
@@ -3510,7 +3511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>57</v>
       </c>
@@ -3529,15 +3530,15 @@
       <c r="G56" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="H56" s="9"/>
-      <c r="K56" s="7" t="s">
+      <c r="H56" s="6"/>
+      <c r="K56" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L56" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>60</v>
       </c>
@@ -3557,7 +3558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>61</v>
       </c>
@@ -3573,17 +3574,17 @@
       <c r="E58" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="G58" s="9" t="s">
+      <c r="G58" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="K58" s="7" t="s">
+      <c r="K58" s="15" t="s">
         <v>50</v>
       </c>
       <c r="L58" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>62</v>
       </c>
@@ -3603,7 +3604,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>63</v>
       </c>
@@ -3619,17 +3620,17 @@
       <c r="E60" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="G60" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="K60" s="7" t="s">
+      <c r="K60" s="15" t="s">
         <v>456</v>
       </c>
       <c r="L60" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>64</v>
       </c>
@@ -3649,7 +3650,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>65</v>
       </c>
@@ -3665,17 +3666,17 @@
       <c r="E62" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="G62" s="9" t="s">
+      <c r="G62" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="K62" s="7" t="s">
+      <c r="K62" s="15" t="s">
         <v>455</v>
       </c>
       <c r="L62" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>66</v>
       </c>
@@ -3695,7 +3696,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>67</v>
       </c>
@@ -3714,14 +3715,14 @@
       <c r="G64" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K64" s="7">
+      <c r="K64" s="15">
         <v>66</v>
       </c>
       <c r="L64" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>68</v>
       </c>
@@ -3740,14 +3741,14 @@
       <c r="G65" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K65" s="7">
+      <c r="K65" s="15">
         <v>66</v>
       </c>
       <c r="L65" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>69</v>
       </c>
@@ -3766,14 +3767,14 @@
       <c r="G66" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K66" s="7">
+      <c r="K66" s="15">
         <v>66</v>
       </c>
       <c r="L66" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>70</v>
       </c>
@@ -3792,14 +3793,14 @@
       <c r="G67" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K67" s="7" t="s">
+      <c r="K67" s="15" t="s">
         <v>51</v>
       </c>
       <c r="L67" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>71</v>
       </c>
@@ -3818,14 +3819,14 @@
       <c r="G68" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K68" s="7" t="s">
+      <c r="K68" s="15" t="s">
         <v>51</v>
       </c>
       <c r="L68" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>72</v>
       </c>
@@ -3845,7 +3846,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>73</v>
       </c>
@@ -3864,14 +3865,14 @@
       <c r="G70" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K70" s="7">
+      <c r="K70" s="15">
         <v>72</v>
       </c>
       <c r="L70" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>74</v>
       </c>
@@ -3890,14 +3891,14 @@
       <c r="G71" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K71" s="7">
+      <c r="K71" s="15">
         <v>72</v>
       </c>
       <c r="L71" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>75</v>
       </c>
@@ -3916,14 +3917,14 @@
       <c r="G72" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K72" s="7">
+      <c r="K72" s="15">
         <v>72</v>
       </c>
       <c r="L72" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>76</v>
       </c>
@@ -3942,17 +3943,17 @@
       <c r="G73" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J73" s="9" t="s">
+      <c r="J73" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K73" s="7">
+      <c r="K73" s="15">
         <v>72</v>
       </c>
       <c r="L73" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>77</v>
       </c>
@@ -3971,14 +3972,14 @@
       <c r="G74" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K74" s="7">
+      <c r="K74" s="15">
         <v>72</v>
       </c>
       <c r="L74" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>78</v>
       </c>
@@ -3997,17 +3998,17 @@
       <c r="G75" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J75" s="9" t="s">
+      <c r="J75" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K75" s="7">
+      <c r="K75" s="15">
         <v>72</v>
       </c>
       <c r="L75" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>79</v>
       </c>
@@ -4026,17 +4027,17 @@
       <c r="G76" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J76" s="9" t="s">
+      <c r="J76" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K76" s="7">
+      <c r="K76" s="15">
         <v>72</v>
       </c>
       <c r="L76" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>80</v>
       </c>
@@ -4055,14 +4056,14 @@
       <c r="G77" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K77" s="7" t="s">
+      <c r="K77" s="15" t="s">
         <v>52</v>
       </c>
       <c r="L77" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>81</v>
       </c>
@@ -4082,7 +4083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>82</v>
       </c>
@@ -4101,14 +4102,14 @@
       <c r="G79" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K79" s="7" t="s">
+      <c r="K79" s="15" t="s">
         <v>454</v>
       </c>
       <c r="L79" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>83</v>
       </c>
@@ -4128,7 +4129,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>84</v>
       </c>
@@ -4147,14 +4148,14 @@
       <c r="G81" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K81" s="7">
+      <c r="K81" s="15">
         <v>83</v>
       </c>
       <c r="L81" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>85</v>
       </c>
@@ -4173,14 +4174,14 @@
       <c r="G82" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K82" s="7">
+      <c r="K82" s="15">
         <v>83</v>
       </c>
       <c r="L82" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>86</v>
       </c>
@@ -4199,14 +4200,14 @@
       <c r="G83" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K83" s="7">
+      <c r="K83" s="15">
         <v>83</v>
       </c>
       <c r="L83" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>87</v>
       </c>
@@ -4225,14 +4226,14 @@
       <c r="G84" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K84" s="7">
+      <c r="K84" s="15">
         <v>83</v>
       </c>
       <c r="L84" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>88</v>
       </c>
@@ -4251,17 +4252,17 @@
       <c r="G85" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J85" s="9" t="s">
+      <c r="J85" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K85" s="7">
+      <c r="K85" s="15">
         <v>83</v>
       </c>
       <c r="L85" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>89</v>
       </c>
@@ -4280,17 +4281,17 @@
       <c r="G86" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J86" s="9" t="s">
+      <c r="J86" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K86" s="7">
+      <c r="K86" s="15">
         <v>83</v>
       </c>
       <c r="L86" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>90</v>
       </c>
@@ -4309,17 +4310,17 @@
       <c r="G87" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J87" s="9" t="s">
+      <c r="J87" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K87" s="7">
+      <c r="K87" s="15">
         <v>83</v>
       </c>
       <c r="L87" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>91</v>
       </c>
@@ -4338,14 +4339,14 @@
       <c r="G88" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="K88" s="7" t="s">
+      <c r="K88" s="15" t="s">
         <v>453</v>
       </c>
       <c r="L88" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>92</v>
       </c>
@@ -4365,7 +4366,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>93</v>
       </c>
@@ -4385,7 +4386,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>94</v>
       </c>
@@ -4404,17 +4405,17 @@
       <c r="G91" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J91" s="9" t="s">
+      <c r="J91" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K91" s="7">
+      <c r="K91" s="15">
         <v>93</v>
       </c>
       <c r="L91" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>95</v>
       </c>
@@ -4433,17 +4434,17 @@
       <c r="G92" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J92" s="9" t="s">
+      <c r="J92" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K92" s="7">
+      <c r="K92" s="15">
         <v>93</v>
       </c>
       <c r="L92" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>96</v>
       </c>
@@ -4462,14 +4463,14 @@
       <c r="G93" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K93" s="7">
+      <c r="K93" s="15">
         <v>93</v>
       </c>
       <c r="L93" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>97</v>
       </c>
@@ -4488,14 +4489,14 @@
       <c r="G94" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="K94" s="7">
+      <c r="K94" s="15">
         <v>93</v>
       </c>
       <c r="L94" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>98</v>
       </c>
@@ -4514,14 +4515,14 @@
       <c r="G95" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="K95" s="7">
+      <c r="K95" s="15">
         <v>93</v>
       </c>
       <c r="L95" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>99</v>
       </c>
@@ -4540,17 +4541,17 @@
       <c r="G96" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J96" s="9" t="s">
+      <c r="J96" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K96" s="7">
+      <c r="K96" s="15">
         <v>93</v>
       </c>
       <c r="L96" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>100</v>
       </c>
@@ -4569,14 +4570,14 @@
       <c r="G97" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K97" s="7" t="s">
+      <c r="K97" s="15" t="s">
         <v>452</v>
       </c>
       <c r="L97" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>101</v>
       </c>
@@ -4596,7 +4597,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>102</v>
       </c>
@@ -4616,7 +4617,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>103</v>
       </c>
@@ -4636,7 +4637,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>104</v>
       </c>
@@ -4655,17 +4656,17 @@
       <c r="G101" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J101" s="9" t="s">
+      <c r="J101" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K101" s="7">
+      <c r="K101" s="15">
         <v>103</v>
       </c>
       <c r="L101" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>105</v>
       </c>
@@ -4684,17 +4685,17 @@
       <c r="G102" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J102" s="9" t="s">
+      <c r="J102" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K102" s="7">
+      <c r="K102" s="15">
         <v>103</v>
       </c>
       <c r="L102" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>106</v>
       </c>
@@ -4713,17 +4714,17 @@
       <c r="G103" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J103" s="9" t="s">
+      <c r="J103" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K103" s="7">
+      <c r="K103" s="15">
         <v>103</v>
       </c>
       <c r="L103" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>107</v>
       </c>
@@ -4742,17 +4743,17 @@
       <c r="G104" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J104" s="9" t="s">
+      <c r="J104" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K104" s="7">
+      <c r="K104" s="15">
         <v>103</v>
       </c>
       <c r="L104" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>108</v>
       </c>
@@ -4771,14 +4772,14 @@
       <c r="G105" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K105" s="7" t="s">
+      <c r="K105" s="15" t="s">
         <v>451</v>
       </c>
       <c r="L105" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>109</v>
       </c>
@@ -4798,7 +4799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>110</v>
       </c>
@@ -4818,7 +4819,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>111</v>
       </c>
@@ -4837,14 +4838,14 @@
       <c r="G108" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="K108" s="7" t="s">
+      <c r="K108" s="15" t="s">
         <v>450</v>
       </c>
       <c r="L108" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>112</v>
       </c>
@@ -4864,7 +4865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>113</v>
       </c>
@@ -4883,14 +4884,14 @@
       <c r="G110" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K110" s="7">
+      <c r="K110" s="15">
         <v>112</v>
       </c>
       <c r="L110" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>114</v>
       </c>
@@ -4909,14 +4910,14 @@
       <c r="G111" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K111" s="7">
+      <c r="K111" s="15">
         <v>112</v>
       </c>
       <c r="L111" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>115</v>
       </c>
@@ -4935,17 +4936,17 @@
       <c r="G112" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J112" s="9" t="s">
+      <c r="J112" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K112" s="7">
+      <c r="K112" s="15">
         <v>112</v>
       </c>
       <c r="L112" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>116</v>
       </c>
@@ -4964,17 +4965,17 @@
       <c r="G113" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J113" s="9" t="s">
+      <c r="J113" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K113" s="7">
+      <c r="K113" s="15">
         <v>112</v>
       </c>
       <c r="L113" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>117</v>
       </c>
@@ -4993,17 +4994,17 @@
       <c r="G114" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J114" s="9" t="s">
+      <c r="J114" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K114" s="7">
+      <c r="K114" s="15">
         <v>112</v>
       </c>
       <c r="L114" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>118</v>
       </c>
@@ -5022,14 +5023,14 @@
       <c r="G115" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K115" s="7" t="s">
+      <c r="K115" s="15" t="s">
         <v>449</v>
       </c>
       <c r="L115" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>119</v>
       </c>
@@ -5049,7 +5050,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>120</v>
       </c>
@@ -5068,12 +5069,9 @@
       <c r="G117" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K117" s="7"/>
-      <c r="L117" s="4" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K117" s="15"/>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>121</v>
       </c>
@@ -5092,14 +5090,14 @@
       <c r="G118" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K118" s="7" t="s">
+      <c r="K118" s="15" t="s">
         <v>521</v>
       </c>
       <c r="L118" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>122</v>
       </c>
@@ -5118,14 +5116,14 @@
       <c r="G119" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K119" s="7" t="s">
+      <c r="K119" s="15" t="s">
         <v>521</v>
       </c>
       <c r="L119" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>123</v>
       </c>
@@ -5144,17 +5142,17 @@
       <c r="G120" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J120" s="9" t="s">
+      <c r="J120" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K120" s="7" t="s">
+      <c r="K120" s="15" t="s">
         <v>521</v>
       </c>
       <c r="L120" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>124</v>
       </c>
@@ -5173,14 +5171,14 @@
       <c r="G121" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K121" s="7" t="s">
+      <c r="K121" s="15" t="s">
         <v>521</v>
       </c>
       <c r="L121" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>125</v>
       </c>
@@ -5199,17 +5197,17 @@
       <c r="G122" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J122" s="9" t="s">
+      <c r="J122" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K122" s="7" t="s">
+      <c r="K122" s="15" t="s">
         <v>521</v>
       </c>
       <c r="L122" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>126</v>
       </c>
@@ -5228,17 +5226,17 @@
       <c r="G123" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J123" s="9" t="s">
+      <c r="J123" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K123" s="7" t="s">
+      <c r="K123" s="15" t="s">
         <v>521</v>
       </c>
       <c r="L123" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>127</v>
       </c>
@@ -5257,14 +5255,14 @@
       <c r="G124" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K124" s="7" t="s">
+      <c r="K124" s="15" t="s">
         <v>448</v>
       </c>
       <c r="L124" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>128</v>
       </c>
@@ -5284,7 +5282,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>129</v>
       </c>
@@ -5303,14 +5301,14 @@
       <c r="G126" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K126" s="7">
+      <c r="K126" s="15">
         <v>128</v>
       </c>
       <c r="L126" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>130</v>
       </c>
@@ -5329,14 +5327,14 @@
       <c r="G127" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K127" s="7">
+      <c r="K127" s="15">
         <v>128</v>
       </c>
       <c r="L127" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>131</v>
       </c>
@@ -5355,14 +5353,14 @@
       <c r="G128" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K128" s="7">
+      <c r="K128" s="15">
         <v>128</v>
       </c>
       <c r="L128" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>132</v>
       </c>
@@ -5381,14 +5379,14 @@
       <c r="G129" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K129" s="7">
+      <c r="K129" s="15">
         <v>128</v>
       </c>
       <c r="L129" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>133</v>
       </c>
@@ -5407,14 +5405,14 @@
       <c r="G130" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K130" s="7">
+      <c r="K130" s="15">
         <v>128</v>
       </c>
       <c r="L130" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>134</v>
       </c>
@@ -5433,17 +5431,17 @@
       <c r="G131" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J131" s="9" t="s">
+      <c r="J131" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K131" s="7">
+      <c r="K131" s="15">
         <v>128</v>
       </c>
       <c r="L131" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>135</v>
       </c>
@@ -5462,17 +5460,17 @@
       <c r="G132" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J132" s="9" t="s">
+      <c r="J132" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K132" s="7">
+      <c r="K132" s="15">
         <v>128</v>
       </c>
       <c r="L132" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>136</v>
       </c>
@@ -5492,7 +5490,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>137</v>
       </c>
@@ -5511,14 +5509,14 @@
       <c r="G134" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K134" s="7">
+      <c r="K134" s="15">
         <v>136</v>
       </c>
       <c r="L134" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>138</v>
       </c>
@@ -5537,14 +5535,14 @@
       <c r="G135" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K135" s="7">
+      <c r="K135" s="15">
         <v>136</v>
       </c>
       <c r="L135" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>139</v>
       </c>
@@ -5563,17 +5561,17 @@
       <c r="G136" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J136" s="9" t="s">
+      <c r="J136" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K136" s="7">
+      <c r="K136" s="15">
         <v>136</v>
       </c>
       <c r="L136" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>140</v>
       </c>
@@ -5592,17 +5590,17 @@
       <c r="G137" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J137" s="9" t="s">
+      <c r="J137" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K137" s="7">
+      <c r="K137" s="15">
         <v>136</v>
       </c>
       <c r="L137" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>141</v>
       </c>
@@ -5622,7 +5620,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>142</v>
       </c>
@@ -5641,14 +5639,14 @@
       <c r="G139" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K139" s="7">
+      <c r="K139" s="15">
         <v>141</v>
       </c>
       <c r="L139" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>143</v>
       </c>
@@ -5667,17 +5665,17 @@
       <c r="G140" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J140" s="9" t="s">
+      <c r="J140" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K140" s="7">
+      <c r="K140" s="15">
         <v>141</v>
       </c>
       <c r="L140" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>144</v>
       </c>
@@ -5696,17 +5694,17 @@
       <c r="G141" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J141" s="9" t="s">
+      <c r="J141" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K141" s="7">
+      <c r="K141" s="15">
         <v>141</v>
       </c>
       <c r="L141" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>145</v>
       </c>
@@ -5726,7 +5724,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>146</v>
       </c>
@@ -5745,14 +5743,14 @@
       <c r="G143" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K143" s="7">
+      <c r="K143" s="15">
         <v>145</v>
       </c>
       <c r="L143" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>147</v>
       </c>
@@ -5771,17 +5769,17 @@
       <c r="G144" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J144" s="9" t="s">
+      <c r="J144" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K144" s="7">
+      <c r="K144" s="15">
         <v>145</v>
       </c>
       <c r="L144" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>148</v>
       </c>
@@ -5800,17 +5798,17 @@
       <c r="G145" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J145" s="9" t="s">
+      <c r="J145" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K145" s="7">
+      <c r="K145" s="15">
         <v>145</v>
       </c>
       <c r="L145" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>149</v>
       </c>
@@ -5830,7 +5828,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>150</v>
       </c>
@@ -5849,14 +5847,14 @@
       <c r="G147" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K147" s="7">
+      <c r="K147" s="15">
         <v>149</v>
       </c>
       <c r="L147" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>151</v>
       </c>
@@ -5875,14 +5873,14 @@
       <c r="G148" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K148" s="7" t="s">
+      <c r="K148" s="15" t="s">
         <v>447</v>
       </c>
       <c r="L148" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>152</v>
       </c>
@@ -5901,17 +5899,17 @@
       <c r="G149" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J149" s="9" t="s">
+      <c r="J149" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K149" s="7">
+      <c r="K149" s="15">
         <v>149</v>
       </c>
       <c r="L149" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>153</v>
       </c>
@@ -5930,17 +5928,17 @@
       <c r="G150" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J150" s="9" t="s">
+      <c r="J150" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K150" s="7">
+      <c r="K150" s="15">
         <v>149</v>
       </c>
       <c r="L150" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>154</v>
       </c>
@@ -5959,14 +5957,14 @@
       <c r="G151" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K151" s="7">
+      <c r="K151" s="15">
         <v>149</v>
       </c>
       <c r="L151" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>155</v>
       </c>
@@ -5985,11 +5983,11 @@
       <c r="G152" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J152" s="9" t="s">
+      <c r="J152" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>156</v>
       </c>
@@ -6008,14 +6006,14 @@
       <c r="G153" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K153" s="7">
+      <c r="K153" s="15">
         <v>155</v>
       </c>
       <c r="L153" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>157</v>
       </c>
@@ -6035,7 +6033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>158</v>
       </c>
@@ -6054,14 +6052,14 @@
       <c r="G155" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K155" s="7">
+      <c r="K155" s="15">
         <v>157</v>
       </c>
       <c r="L155" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>159</v>
       </c>
@@ -6081,7 +6079,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>160</v>
       </c>
@@ -6100,17 +6098,17 @@
       <c r="G157" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J157" s="9" t="s">
+      <c r="J157" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K157" s="7">
+      <c r="K157" s="15">
         <v>159</v>
       </c>
       <c r="L157" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>161</v>
       </c>
@@ -6129,14 +6127,14 @@
       <c r="G158" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K158" s="7">
+      <c r="K158" s="15">
         <v>159</v>
       </c>
       <c r="L158" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>162</v>
       </c>
@@ -6155,17 +6153,17 @@
       <c r="G159" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J159" s="9" t="s">
+      <c r="J159" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K159" s="7">
+      <c r="K159" s="15">
         <v>159</v>
       </c>
       <c r="L159" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>163</v>
       </c>
@@ -6184,17 +6182,17 @@
       <c r="G160" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J160" s="9" t="s">
+      <c r="J160" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K160" s="7">
+      <c r="K160" s="15">
         <v>159</v>
       </c>
       <c r="L160" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>164</v>
       </c>
@@ -6213,14 +6211,14 @@
       <c r="G161" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K161" s="7">
+      <c r="K161" s="15">
         <v>163</v>
       </c>
       <c r="L161" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>165</v>
       </c>
@@ -6240,7 +6238,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>166</v>
       </c>
@@ -6260,7 +6258,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>167</v>
       </c>
@@ -6279,14 +6277,14 @@
       <c r="G164" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K164" s="7">
+      <c r="K164" s="15">
         <v>166</v>
       </c>
       <c r="L164" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>168</v>
       </c>
@@ -6305,17 +6303,17 @@
       <c r="G165" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J165" s="9" t="s">
+      <c r="J165" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K165" s="7">
+      <c r="K165" s="15">
         <v>167</v>
       </c>
       <c r="L165" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>169</v>
       </c>
@@ -6334,17 +6332,17 @@
       <c r="G166" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J166" s="9" t="s">
+      <c r="J166" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K166" s="7">
+      <c r="K166" s="15">
         <v>167</v>
       </c>
       <c r="L166" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>170</v>
       </c>
@@ -6360,17 +6358,17 @@
       <c r="E167" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="G167" s="9" t="s">
+      <c r="G167" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="K167" s="7">
+      <c r="K167" s="15">
         <v>167</v>
       </c>
       <c r="L167" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>171</v>
       </c>
@@ -6389,17 +6387,17 @@
       <c r="G168" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="J168" s="9" t="s">
+      <c r="J168" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K168" s="7">
+      <c r="K168" s="15">
         <v>167</v>
       </c>
       <c r="L168" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>172</v>
       </c>
@@ -6418,17 +6416,17 @@
       <c r="G169" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J169" s="9" t="s">
+      <c r="J169" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K169" s="7">
+      <c r="K169" s="15">
         <v>167</v>
       </c>
       <c r="L169" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>173</v>
       </c>
@@ -6447,14 +6445,14 @@
       <c r="G170" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="K170" s="7">
+      <c r="K170" s="15">
         <v>172</v>
       </c>
       <c r="L170" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>174</v>
       </c>
@@ -6474,7 +6472,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>175</v>
       </c>
@@ -6493,14 +6491,14 @@
       <c r="G172" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K172" s="7">
+      <c r="K172" s="15">
         <v>174</v>
       </c>
       <c r="L172" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>176</v>
       </c>
@@ -6519,14 +6517,14 @@
       <c r="G173" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K173" s="7">
+      <c r="K173" s="15">
         <v>174</v>
       </c>
       <c r="L173" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>177</v>
       </c>
@@ -6545,14 +6543,14 @@
       <c r="G174" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K174" s="7">
+      <c r="K174" s="15">
         <v>174</v>
       </c>
       <c r="L174" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>178</v>
       </c>
@@ -6571,14 +6569,14 @@
       <c r="G175" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K175" s="7">
+      <c r="K175" s="15">
         <v>174</v>
       </c>
       <c r="L175" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>179</v>
       </c>
@@ -6597,14 +6595,14 @@
       <c r="G176" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K176" s="7">
+      <c r="K176" s="15">
         <v>174</v>
       </c>
       <c r="L176" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>180</v>
       </c>
@@ -6623,14 +6621,14 @@
       <c r="G177" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K177" s="7">
+      <c r="K177" s="15">
         <v>174</v>
       </c>
       <c r="L177" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>181</v>
       </c>
@@ -6646,20 +6644,20 @@
       <c r="E178" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="G178" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J178" s="9" t="s">
+      <c r="G178" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J178" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K178" s="7">
+      <c r="K178" s="15">
         <v>180</v>
       </c>
       <c r="L178" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>182</v>
       </c>
@@ -6678,17 +6676,17 @@
       <c r="G179" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J179" s="9" t="s">
+      <c r="J179" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K179" s="7">
+      <c r="K179" s="15">
         <v>180</v>
       </c>
       <c r="L179" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>183</v>
       </c>
@@ -6707,14 +6705,14 @@
       <c r="G180" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K180" s="7">
+      <c r="K180" s="15">
         <v>182</v>
       </c>
       <c r="L180" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>184</v>
       </c>
@@ -6734,7 +6732,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
         <v>185</v>
       </c>
@@ -6753,14 +6751,14 @@
       <c r="G182" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="K182" s="7">
+      <c r="K182" s="15">
         <v>184</v>
       </c>
       <c r="L182" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>186</v>
       </c>
@@ -6779,14 +6777,14 @@
       <c r="G183" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K183" s="7">
+      <c r="K183" s="15">
         <v>184</v>
       </c>
       <c r="L183" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>187</v>
       </c>
@@ -6805,14 +6803,14 @@
       <c r="G184" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K184" s="7">
+      <c r="K184" s="15">
         <v>184</v>
       </c>
       <c r="L184" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>188</v>
       </c>
@@ -6831,14 +6829,14 @@
       <c r="G185" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K185" s="7">
+      <c r="K185" s="15">
         <v>184</v>
       </c>
       <c r="L185" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>189</v>
       </c>
@@ -6857,14 +6855,14 @@
       <c r="G186" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K186" s="7">
+      <c r="K186" s="15">
         <v>188</v>
       </c>
       <c r="L186" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>190</v>
       </c>
@@ -6883,17 +6881,17 @@
       <c r="G187" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J187" s="9" t="s">
+      <c r="J187" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K187" s="7">
+      <c r="K187" s="15">
         <v>188</v>
       </c>
       <c r="L187" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>191</v>
       </c>
@@ -6912,14 +6910,14 @@
       <c r="G188" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="K188" s="7">
+      <c r="K188" s="15">
         <v>190</v>
       </c>
       <c r="L188" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>192</v>
       </c>
@@ -6939,7 +6937,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>193</v>
       </c>
@@ -6958,14 +6956,14 @@
       <c r="G190" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K190" s="7">
+      <c r="K190" s="15">
         <v>192</v>
       </c>
       <c r="L190" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>194</v>
       </c>
@@ -6984,14 +6982,14 @@
       <c r="G191" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K191" s="7">
+      <c r="K191" s="15">
         <v>192</v>
       </c>
       <c r="L191" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>195</v>
       </c>
@@ -7010,14 +7008,14 @@
       <c r="G192" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K192" s="7">
+      <c r="K192" s="15">
         <v>192</v>
       </c>
       <c r="L192" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>196</v>
       </c>
@@ -7036,14 +7034,14 @@
       <c r="G193" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K193" s="7">
+      <c r="K193" s="15">
         <v>192</v>
       </c>
       <c r="L193" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>197</v>
       </c>
@@ -7062,17 +7060,17 @@
       <c r="G194" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J194" s="9" t="s">
+      <c r="J194" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K194" s="7">
+      <c r="K194" s="15">
         <v>193</v>
       </c>
       <c r="L194" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>198</v>
       </c>
@@ -7091,14 +7089,14 @@
       <c r="G195" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K195" s="7">
+      <c r="K195" s="15">
         <v>193</v>
       </c>
       <c r="L195" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
         <v>199</v>
       </c>
@@ -7118,7 +7116,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>200</v>
       </c>
@@ -7137,14 +7135,14 @@
       <c r="G197" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K197" s="7">
+      <c r="K197" s="15">
         <v>199</v>
       </c>
       <c r="L197" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>201</v>
       </c>
@@ -7163,18 +7161,18 @@
       <c r="G198" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J198" s="9" t="s">
+      <c r="J198" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K198" s="7">
+      <c r="K198" s="15">
         <v>199</v>
       </c>
       <c r="L198" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A199" s="9">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A199" s="6">
         <v>202</v>
       </c>
       <c r="B199" s="4" t="s">
@@ -7192,7 +7190,7 @@
       <c r="G199" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="K199" s="7">
+      <c r="K199" s="15">
         <v>201</v>
       </c>
       <c r="L199" s="4" t="s">
@@ -7208,207 +7206,207 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5B0D63-9F6C-44CA-87BF-274BCE12F441}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="57" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="8" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="10" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="10" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="10" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="10" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="12" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="10" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="10" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="10" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="10" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="10" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="10" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="10" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="12" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="10" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="12" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="10" t="s">
         <v>502</v>
       </c>
     </row>

--- a/dataland-framework-toolbox/inputs/lksg/lksg.xlsx
+++ b/dataland-framework-toolbox/inputs/lksg/lksg.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dataland\Dataland\dataland-framework-toolbox\inputs\lksg\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d92928\Documents\Projects\Dataland\Dataland\dataland-framework-toolbox\inputs\lksg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F04646A-DBEB-4F6A-A3DC-F411E4ED8CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19602C64-F809-4879-900D-F6CFF5A38965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{64EA21DF-A91B-4C8A-A36C-EACA4F178F40}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{64EA21DF-A91B-4C8A-A36C-EACA4F178F40}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="2" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="513">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -686,9 +686,6 @@
     <t>Unlawful Eviction and Taking of Land - Other Measures Description</t>
   </si>
   <si>
-    <t>Voluntary Guidelines on the Responsible Governance of Tenure</t>
-  </si>
-  <si>
     <t>Use of Private Public Security Forces</t>
   </si>
   <si>
@@ -1242,9 +1239,6 @@
   </si>
   <si>
     <t>Please list other measures (if available) you take to avoid, reduce, mitigate, or remedy direct and indirect adverse impacts on the lands and natural resources of indigenous peoples and local communities.</t>
-  </si>
-  <si>
-    <t>Have you implemented the voluntary guidelines on the responsible governance of tenure in your company?</t>
   </si>
   <si>
     <t>Does your company use private and/or public security forces to protect company projects?</t>
@@ -1613,6 +1607,9 @@
   </si>
   <si>
     <t>LkSG Subcontracting Companies</t>
+  </si>
+  <si>
+    <t>Hazardous Waste Transport Prevention Other Measures Description</t>
   </si>
 </sst>
 </file>
@@ -2105,25 +2102,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBCA27A-793A-4293-9394-36A2BE726731}">
   <dimension ref="A1:M195"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.36328125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="78.453125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="150.90625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="87.36328125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="39.6328125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="23.08984375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="24.90625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="18.453125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="78.44140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="150.88671875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="87.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="39.6640625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="23.109375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="24.88671875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="18.44140625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.08984375" style="4"/>
+    <col min="14" max="16384" width="9.109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2164,7 +2161,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -2184,10 +2181,10 @@
         <v>16</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2201,13 +2198,13 @@
         <v>52</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -2221,13 +2218,13 @@
         <v>53</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2241,20 +2238,20 @@
         <v>54</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K5" s="14">
         <f>A4</f>
         <v>3</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -2268,13 +2265,13 @@
         <v>55</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2288,16 +2285,16 @@
         <v>56</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -2311,13 +2308,13 @@
         <v>57</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2331,22 +2328,22 @@
         <v>58</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -2360,13 +2357,13 @@
         <v>59</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2380,13 +2377,13 @@
         <v>60</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2400,13 +2397,13 @@
         <v>61</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2420,19 +2417,19 @@
         <v>62</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K13" s="14">
         <v>11</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -2446,7 +2443,7 @@
         <v>63</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>20</v>
@@ -2455,10 +2452,10 @@
         <v>11</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2472,19 +2469,19 @@
         <v>64</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="K15" s="15" t="s">
         <v>44</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>16</v>
       </c>
@@ -2498,7 +2495,7 @@
         <v>65</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>20</v>
@@ -2507,10 +2504,10 @@
         <v>11</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>17</v>
       </c>
@@ -2524,19 +2521,19 @@
         <v>66</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>18</v>
       </c>
@@ -2550,19 +2547,19 @@
         <v>67</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>19</v>
       </c>
@@ -2576,22 +2573,22 @@
         <v>68</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>17</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="K19" s="15">
         <v>11</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>20</v>
       </c>
@@ -2605,22 +2602,22 @@
         <v>69</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="K20" s="15">
         <v>11</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>21</v>
       </c>
@@ -2634,19 +2631,19 @@
         <v>70</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="K21" s="15">
         <v>11</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>22</v>
       </c>
@@ -2657,22 +2654,22 @@
         <v>27</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="K22" s="15">
         <v>11</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>23</v>
       </c>
@@ -2686,7 +2683,7 @@
         <v>71</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>20</v>
@@ -2695,7 +2692,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>24</v>
       </c>
@@ -2709,7 +2706,7 @@
         <v>72</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>20</v>
@@ -2718,10 +2715,10 @@
         <v>23</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>25</v>
       </c>
@@ -2735,19 +2732,19 @@
         <v>73</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>26</v>
       </c>
@@ -2761,20 +2758,20 @@
         <v>74</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H26" s="6"/>
       <c r="K26" s="15" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>29</v>
       </c>
@@ -2788,7 +2785,7 @@
         <v>75</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>20</v>
@@ -2797,10 +2794,10 @@
         <v>23</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>30</v>
       </c>
@@ -2814,7 +2811,7 @@
         <v>23</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>20</v>
@@ -2823,7 +2820,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>31</v>
       </c>
@@ -2837,7 +2834,7 @@
         <v>76</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>20</v>
@@ -2846,10 +2843,10 @@
         <v>30</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>32</v>
       </c>
@@ -2863,7 +2860,7 @@
         <v>77</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>20</v>
@@ -2872,10 +2869,10 @@
         <v>30</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>33</v>
       </c>
@@ -2889,7 +2886,7 @@
         <v>78</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>20</v>
@@ -2898,10 +2895,10 @@
         <v>30</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>34</v>
       </c>
@@ -2915,7 +2912,7 @@
         <v>79</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>20</v>
@@ -2924,10 +2921,10 @@
         <v>30</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>35</v>
       </c>
@@ -2941,7 +2938,7 @@
         <v>80</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>20</v>
@@ -2950,10 +2947,10 @@
         <v>30</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>36</v>
       </c>
@@ -2967,22 +2964,22 @@
         <v>81</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="K34" s="15" t="s">
         <v>45</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>37</v>
       </c>
@@ -2996,20 +2993,20 @@
         <v>82</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H35" s="6"/>
       <c r="K35" s="15" t="s">
         <v>45</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>41</v>
       </c>
@@ -3023,7 +3020,7 @@
         <v>83</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>20</v>
@@ -3032,10 +3029,10 @@
         <v>30</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>42</v>
       </c>
@@ -3049,7 +3046,7 @@
         <v>84</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>20</v>
@@ -3058,10 +3055,10 @@
         <v>30</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>43</v>
       </c>
@@ -3075,7 +3072,7 @@
         <v>85</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>20</v>
@@ -3084,10 +3081,10 @@
         <v>30</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>44</v>
       </c>
@@ -3101,7 +3098,7 @@
         <v>86</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>20</v>
@@ -3110,7 +3107,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>45</v>
       </c>
@@ -3124,7 +3121,7 @@
         <v>87</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>20</v>
@@ -3133,7 +3130,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>46</v>
       </c>
@@ -3147,7 +3144,7 @@
         <v>88</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>20</v>
@@ -3156,10 +3153,10 @@
         <v>46</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>47</v>
       </c>
@@ -3173,7 +3170,7 @@
         <v>89</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>20</v>
@@ -3182,7 +3179,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>48</v>
       </c>
@@ -3196,7 +3193,7 @@
         <v>90</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>20</v>
@@ -3205,7 +3202,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>49</v>
       </c>
@@ -3219,19 +3216,19 @@
         <v>91</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K44" s="15" t="s">
         <v>47</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>50</v>
       </c>
@@ -3245,7 +3242,7 @@
         <v>92</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>20</v>
@@ -3254,7 +3251,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>51</v>
       </c>
@@ -3268,7 +3265,7 @@
         <v>93</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>20</v>
@@ -3277,7 +3274,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>52</v>
       </c>
@@ -3291,13 +3288,13 @@
         <v>94</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>53</v>
       </c>
@@ -3311,13 +3308,13 @@
         <v>95</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>54</v>
       </c>
@@ -3331,13 +3328,13 @@
         <v>96</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>55</v>
       </c>
@@ -3351,13 +3348,13 @@
         <v>97</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>56</v>
       </c>
@@ -3371,13 +3368,13 @@
         <v>98</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>57</v>
       </c>
@@ -3391,20 +3388,20 @@
         <v>99</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H52" s="6"/>
       <c r="K52" s="15" t="s">
         <v>48</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>60</v>
       </c>
@@ -3418,13 +3415,13 @@
         <v>100</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>61</v>
       </c>
@@ -3438,19 +3435,19 @@
         <v>101</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="K54" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>62</v>
       </c>
@@ -3464,13 +3461,13 @@
         <v>102</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>63</v>
       </c>
@@ -3484,19 +3481,19 @@
         <v>103</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>64</v>
       </c>
@@ -3510,13 +3507,13 @@
         <v>104</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>65</v>
       </c>
@@ -3530,19 +3527,19 @@
         <v>105</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>66</v>
       </c>
@@ -3556,13 +3553,13 @@
         <v>106</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>67</v>
       </c>
@@ -3576,7 +3573,7 @@
         <v>107</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>20</v>
@@ -3585,10 +3582,10 @@
         <v>66</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>68</v>
       </c>
@@ -3602,7 +3599,7 @@
         <v>108</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>20</v>
@@ -3611,10 +3608,10 @@
         <v>66</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>69</v>
       </c>
@@ -3628,7 +3625,7 @@
         <v>110</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>20</v>
@@ -3637,10 +3634,10 @@
         <v>66</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>70</v>
       </c>
@@ -3654,7 +3651,7 @@
         <v>109</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>20</v>
@@ -3663,10 +3660,10 @@
         <v>50</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>71</v>
       </c>
@@ -3680,19 +3677,19 @@
         <v>111</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="K64" s="15" t="s">
-        <v>50</v>
+        <v>433</v>
+      </c>
+      <c r="K64" s="15">
+        <v>70</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>72</v>
       </c>
@@ -3706,13 +3703,13 @@
         <v>112</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>73</v>
       </c>
@@ -3726,7 +3723,7 @@
         <v>113</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>20</v>
@@ -3735,10 +3732,10 @@
         <v>72</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>74</v>
       </c>
@@ -3752,7 +3749,7 @@
         <v>114</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>20</v>
@@ -3761,10 +3758,10 @@
         <v>72</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>75</v>
       </c>
@@ -3778,7 +3775,7 @@
         <v>115</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>20</v>
@@ -3787,10 +3784,10 @@
         <v>72</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>76</v>
       </c>
@@ -3804,7 +3801,7 @@
         <v>116</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>20</v>
@@ -3816,10 +3813,10 @@
         <v>72</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>77</v>
       </c>
@@ -3833,7 +3830,7 @@
         <v>117</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>20</v>
@@ -3842,10 +3839,10 @@
         <v>72</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>78</v>
       </c>
@@ -3859,7 +3856,7 @@
         <v>118</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>20</v>
@@ -3871,10 +3868,10 @@
         <v>72</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>79</v>
       </c>
@@ -3888,7 +3885,7 @@
         <v>119</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>20</v>
@@ -3900,10 +3897,10 @@
         <v>72</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>80</v>
       </c>
@@ -3917,19 +3914,19 @@
         <v>120</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K73" s="15" t="s">
         <v>51</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>81</v>
       </c>
@@ -3943,13 +3940,13 @@
         <v>121</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>82</v>
       </c>
@@ -3963,19 +3960,19 @@
         <v>122</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>83</v>
       </c>
@@ -3989,13 +3986,13 @@
         <v>123</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>84</v>
       </c>
@@ -4009,7 +4006,7 @@
         <v>124</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>20</v>
@@ -4018,10 +4015,10 @@
         <v>83</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>85</v>
       </c>
@@ -4035,7 +4032,7 @@
         <v>125</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>20</v>
@@ -4044,10 +4041,10 @@
         <v>83</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>86</v>
       </c>
@@ -4061,7 +4058,7 @@
         <v>126</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>20</v>
@@ -4070,10 +4067,10 @@
         <v>83</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>87</v>
       </c>
@@ -4087,7 +4084,7 @@
         <v>127</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>20</v>
@@ -4096,10 +4093,10 @@
         <v>83</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>88</v>
       </c>
@@ -4113,7 +4110,7 @@
         <v>128</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>20</v>
@@ -4125,10 +4122,10 @@
         <v>83</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>89</v>
       </c>
@@ -4142,7 +4139,7 @@
         <v>129</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>20</v>
@@ -4154,10 +4151,10 @@
         <v>83</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>90</v>
       </c>
@@ -4171,7 +4168,7 @@
         <v>130</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>20</v>
@@ -4183,10 +4180,10 @@
         <v>83</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>91</v>
       </c>
@@ -4200,19 +4197,19 @@
         <v>131</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="K84" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>92</v>
       </c>
@@ -4226,13 +4223,13 @@
         <v>132</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>93</v>
       </c>
@@ -4246,13 +4243,13 @@
         <v>133</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>94</v>
       </c>
@@ -4266,7 +4263,7 @@
         <v>134</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>20</v>
@@ -4278,10 +4275,10 @@
         <v>93</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>95</v>
       </c>
@@ -4295,7 +4292,7 @@
         <v>135</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G88" s="4" t="s">
         <v>20</v>
@@ -4307,10 +4304,10 @@
         <v>93</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>96</v>
       </c>
@@ -4324,7 +4321,7 @@
         <v>136</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>20</v>
@@ -4333,10 +4330,10 @@
         <v>93</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>97</v>
       </c>
@@ -4350,19 +4347,19 @@
         <v>137</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="K90" s="15">
         <v>93</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>98</v>
       </c>
@@ -4376,19 +4373,19 @@
         <v>138</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="K91" s="15">
         <v>93</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>99</v>
       </c>
@@ -4402,7 +4399,7 @@
         <v>139</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>20</v>
@@ -4414,10 +4411,10 @@
         <v>93</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>100</v>
       </c>
@@ -4431,19 +4428,19 @@
         <v>140</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K93" s="15" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>101</v>
       </c>
@@ -4457,13 +4454,13 @@
         <v>141</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G94" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>102</v>
       </c>
@@ -4477,13 +4474,13 @@
         <v>142</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>103</v>
       </c>
@@ -4497,13 +4494,13 @@
         <v>143</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>104</v>
       </c>
@@ -4517,7 +4514,7 @@
         <v>144</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G97" s="4" t="s">
         <v>20</v>
@@ -4529,10 +4526,10 @@
         <v>103</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>105</v>
       </c>
@@ -4546,7 +4543,7 @@
         <v>145</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G98" s="4" t="s">
         <v>20</v>
@@ -4558,10 +4555,10 @@
         <v>103</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>106</v>
       </c>
@@ -4575,7 +4572,7 @@
         <v>146</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G99" s="4" t="s">
         <v>20</v>
@@ -4587,10 +4584,10 @@
         <v>103</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>107</v>
       </c>
@@ -4604,7 +4601,7 @@
         <v>147</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>20</v>
@@ -4616,10 +4613,10 @@
         <v>103</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>108</v>
       </c>
@@ -4633,19 +4630,19 @@
         <v>148</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K101" s="15" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>109</v>
       </c>
@@ -4659,13 +4656,13 @@
         <v>149</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>110</v>
       </c>
@@ -4679,13 +4676,13 @@
         <v>150</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>111</v>
       </c>
@@ -4699,19 +4696,19 @@
         <v>151</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K104" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>112</v>
       </c>
@@ -4725,13 +4722,13 @@
         <v>152</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G105" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>113</v>
       </c>
@@ -4745,7 +4742,7 @@
         <v>153</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G106" s="4" t="s">
         <v>20</v>
@@ -4754,10 +4751,10 @@
         <v>112</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>114</v>
       </c>
@@ -4771,7 +4768,7 @@
         <v>154</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G107" s="4" t="s">
         <v>20</v>
@@ -4780,10 +4777,10 @@
         <v>112</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>115</v>
       </c>
@@ -4797,7 +4794,7 @@
         <v>155</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G108" s="4" t="s">
         <v>20</v>
@@ -4809,10 +4806,10 @@
         <v>112</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>116</v>
       </c>
@@ -4826,7 +4823,7 @@
         <v>156</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G109" s="4" t="s">
         <v>20</v>
@@ -4838,10 +4835,10 @@
         <v>112</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>117</v>
       </c>
@@ -4855,7 +4852,7 @@
         <v>157</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G110" s="4" t="s">
         <v>20</v>
@@ -4867,10 +4864,10 @@
         <v>112</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>118</v>
       </c>
@@ -4884,19 +4881,19 @@
         <v>158</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K111" s="15" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>119</v>
       </c>
@@ -4910,13 +4907,13 @@
         <v>159</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>120</v>
       </c>
@@ -4930,14 +4927,14 @@
         <v>160</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G113" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K113" s="15"/>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>121</v>
       </c>
@@ -4951,19 +4948,19 @@
         <v>161</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G114" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K114" s="15" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>122</v>
       </c>
@@ -4977,19 +4974,19 @@
         <v>162</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G115" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K115" s="15" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>123</v>
       </c>
@@ -5003,7 +5000,7 @@
         <v>163</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G116" s="4" t="s">
         <v>20</v>
@@ -5012,13 +5009,13 @@
         <v>22</v>
       </c>
       <c r="K116" s="15" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>124</v>
       </c>
@@ -5032,19 +5029,19 @@
         <v>164</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G117" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K117" s="15" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>125</v>
       </c>
@@ -5058,7 +5055,7 @@
         <v>165</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G118" s="4" t="s">
         <v>20</v>
@@ -5067,13 +5064,13 @@
         <v>22</v>
       </c>
       <c r="K118" s="15" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>126</v>
       </c>
@@ -5087,7 +5084,7 @@
         <v>166</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G119" s="4" t="s">
         <v>20</v>
@@ -5096,13 +5093,13 @@
         <v>22</v>
       </c>
       <c r="K119" s="15" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="L119" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>127</v>
       </c>
@@ -5116,19 +5113,19 @@
         <v>167</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K120" s="15" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>128</v>
       </c>
@@ -5142,13 +5139,13 @@
         <v>168</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G121" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>129</v>
       </c>
@@ -5162,7 +5159,7 @@
         <v>169</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G122" s="4" t="s">
         <v>20</v>
@@ -5171,10 +5168,10 @@
         <v>128</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>130</v>
       </c>
@@ -5188,7 +5185,7 @@
         <v>170</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G123" s="4" t="s">
         <v>20</v>
@@ -5197,10 +5194,10 @@
         <v>128</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>131</v>
       </c>
@@ -5214,7 +5211,7 @@
         <v>171</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G124" s="4" t="s">
         <v>20</v>
@@ -5223,10 +5220,10 @@
         <v>128</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>132</v>
       </c>
@@ -5240,7 +5237,7 @@
         <v>172</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>20</v>
@@ -5249,10 +5246,10 @@
         <v>128</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>133</v>
       </c>
@@ -5266,7 +5263,7 @@
         <v>173</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G126" s="4" t="s">
         <v>20</v>
@@ -5275,10 +5272,10 @@
         <v>128</v>
       </c>
       <c r="L126" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>134</v>
       </c>
@@ -5292,7 +5289,7 @@
         <v>174</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>20</v>
@@ -5304,10 +5301,10 @@
         <v>128</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>135</v>
       </c>
@@ -5321,7 +5318,7 @@
         <v>175</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>20</v>
@@ -5333,10 +5330,10 @@
         <v>128</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>136</v>
       </c>
@@ -5350,13 +5347,13 @@
         <v>176</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>137</v>
       </c>
@@ -5370,7 +5367,7 @@
         <v>177</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G130" s="4" t="s">
         <v>20</v>
@@ -5379,10 +5376,10 @@
         <v>136</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>138</v>
       </c>
@@ -5396,7 +5393,7 @@
         <v>178</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>20</v>
@@ -5405,10 +5402,10 @@
         <v>136</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>139</v>
       </c>
@@ -5422,7 +5419,7 @@
         <v>179</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>20</v>
@@ -5434,10 +5431,10 @@
         <v>136</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>140</v>
       </c>
@@ -5451,7 +5448,7 @@
         <v>180</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>20</v>
@@ -5463,10 +5460,10 @@
         <v>136</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>141</v>
       </c>
@@ -5480,13 +5477,13 @@
         <v>181</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>142</v>
       </c>
@@ -5500,7 +5497,7 @@
         <v>182</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G135" s="4" t="s">
         <v>20</v>
@@ -5509,10 +5506,10 @@
         <v>141</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>143</v>
       </c>
@@ -5526,7 +5523,7 @@
         <v>183</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>20</v>
@@ -5538,10 +5535,10 @@
         <v>141</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>144</v>
       </c>
@@ -5555,7 +5552,7 @@
         <v>184</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>20</v>
@@ -5567,10 +5564,10 @@
         <v>141</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>145</v>
       </c>
@@ -5584,13 +5581,13 @@
         <v>185</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>146</v>
       </c>
@@ -5604,7 +5601,7 @@
         <v>186</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>20</v>
@@ -5613,10 +5610,10 @@
         <v>145</v>
       </c>
       <c r="L139" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>147</v>
       </c>
@@ -5630,7 +5627,7 @@
         <v>187</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G140" s="4" t="s">
         <v>20</v>
@@ -5642,10 +5639,10 @@
         <v>145</v>
       </c>
       <c r="L140" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>148</v>
       </c>
@@ -5659,7 +5656,7 @@
         <v>188</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>20</v>
@@ -5671,10 +5668,10 @@
         <v>145</v>
       </c>
       <c r="L141" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>149</v>
       </c>
@@ -5688,13 +5685,13 @@
         <v>189</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>150</v>
       </c>
@@ -5708,7 +5705,7 @@
         <v>190</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>20</v>
@@ -5717,10 +5714,10 @@
         <v>149</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>151</v>
       </c>
@@ -5734,19 +5731,19 @@
         <v>191</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K144" s="15" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L144" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>152</v>
       </c>
@@ -5760,7 +5757,7 @@
         <v>192</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>20</v>
@@ -5772,10 +5769,10 @@
         <v>149</v>
       </c>
       <c r="L145" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>153</v>
       </c>
@@ -5789,7 +5786,7 @@
         <v>193</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>20</v>
@@ -5801,10 +5798,10 @@
         <v>149</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>154</v>
       </c>
@@ -5818,7 +5815,7 @@
         <v>194</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>20</v>
@@ -5827,10 +5824,10 @@
         <v>149</v>
       </c>
       <c r="L147" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>155</v>
       </c>
@@ -5844,7 +5841,7 @@
         <v>195</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>20</v>
@@ -5853,7 +5850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>156</v>
       </c>
@@ -5867,19 +5864,19 @@
         <v>196</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K149" s="15">
         <v>155</v>
       </c>
       <c r="L149" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>157</v>
       </c>
@@ -5893,13 +5890,13 @@
         <v>197</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>158</v>
       </c>
@@ -5913,19 +5910,19 @@
         <v>198</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K151" s="15">
         <v>157</v>
       </c>
       <c r="L151" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>159</v>
       </c>
@@ -5939,13 +5936,13 @@
         <v>199</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G152" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>160</v>
       </c>
@@ -5959,7 +5956,7 @@
         <v>200</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G153" s="4" t="s">
         <v>20</v>
@@ -5971,10 +5968,10 @@
         <v>159</v>
       </c>
       <c r="L153" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>161</v>
       </c>
@@ -5988,7 +5985,7 @@
         <v>201</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G154" s="4" t="s">
         <v>20</v>
@@ -5997,10 +5994,10 @@
         <v>159</v>
       </c>
       <c r="L154" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>162</v>
       </c>
@@ -6014,7 +6011,7 @@
         <v>202</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>20</v>
@@ -6026,10 +6023,10 @@
         <v>159</v>
       </c>
       <c r="L155" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>163</v>
       </c>
@@ -6043,7 +6040,7 @@
         <v>203</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G156" s="4" t="s">
         <v>20</v>
@@ -6055,10 +6052,10 @@
         <v>159</v>
       </c>
       <c r="L156" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>164</v>
       </c>
@@ -6072,41 +6069,41 @@
         <v>204</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K157" s="15">
         <v>163</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>205</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>21</v>
@@ -6118,15 +6115,21 @@
         <v>206</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>392</v>
+        <v>431</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K159" s="15">
+        <v>166</v>
+      </c>
+      <c r="L159" s="4" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>21</v>
@@ -6138,21 +6141,24 @@
         <v>207</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>433</v>
+        <v>391</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="J160" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="K160" s="15">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L160" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>21</v>
@@ -6164,7 +6170,7 @@
         <v>208</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>20</v>
@@ -6176,12 +6182,12 @@
         <v>167</v>
       </c>
       <c r="L161" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>21</v>
@@ -6193,24 +6199,21 @@
         <v>209</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="G162" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J162" s="6" t="s">
-        <v>22</v>
+        <v>393</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>492</v>
       </c>
       <c r="K162" s="15">
         <v>167</v>
       </c>
       <c r="L162" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>21</v>
@@ -6222,21 +6225,24 @@
         <v>210</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="G163" s="6" t="s">
-        <v>494</v>
+        <v>394</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="J163" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="K163" s="15">
         <v>167</v>
       </c>
       <c r="L163" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>21</v>
@@ -6248,10 +6254,10 @@
         <v>211</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>494</v>
+        <v>20</v>
       </c>
       <c r="J164" s="6" t="s">
         <v>22</v>
@@ -6260,12 +6266,12 @@
         <v>167</v>
       </c>
       <c r="L164" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>21</v>
@@ -6277,50 +6283,41 @@
         <v>212</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J165" s="6" t="s">
-        <v>22</v>
+        <v>504</v>
       </c>
       <c r="K165" s="15">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L165" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>213</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="K166" s="15">
-        <v>172</v>
-      </c>
-      <c r="L166" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>18</v>
@@ -6332,15 +6329,21 @@
         <v>214</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K167" s="15">
+        <v>174</v>
+      </c>
+      <c r="L167" s="4" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>18</v>
@@ -6352,7 +6355,7 @@
         <v>215</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>20</v>
@@ -6361,12 +6364,12 @@
         <v>174</v>
       </c>
       <c r="L168" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>18</v>
@@ -6378,7 +6381,7 @@
         <v>216</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>20</v>
@@ -6387,12 +6390,12 @@
         <v>174</v>
       </c>
       <c r="L169" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>18</v>
@@ -6404,7 +6407,7 @@
         <v>217</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>20</v>
@@ -6413,12 +6416,12 @@
         <v>174</v>
       </c>
       <c r="L170" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>18</v>
@@ -6430,7 +6433,7 @@
         <v>218</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>20</v>
@@ -6439,12 +6442,12 @@
         <v>174</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>18</v>
@@ -6456,7 +6459,7 @@
         <v>219</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>20</v>
@@ -6465,12 +6468,12 @@
         <v>174</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>18</v>
@@ -6482,21 +6485,24 @@
         <v>220</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="G173" s="4" t="s">
-        <v>20</v>
+        <v>404</v>
+      </c>
+      <c r="G173" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J173" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="K173" s="15">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>18</v>
@@ -6508,9 +6514,9 @@
         <v>221</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="G174" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="G174" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J174" s="6" t="s">
@@ -6520,12 +6526,12 @@
         <v>180</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>18</v>
@@ -6537,50 +6543,41 @@
         <v>222</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J175" s="6" t="s">
-        <v>22</v>
+        <v>433</v>
       </c>
       <c r="K175" s="15">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>223</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="K176" s="15">
-        <v>182</v>
-      </c>
-      <c r="L176" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>18</v>
@@ -6592,15 +6589,21 @@
         <v>224</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
+        <v>433</v>
+      </c>
+      <c r="K177" s="15">
+        <v>184</v>
+      </c>
+      <c r="L177" s="4" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>18</v>
@@ -6612,21 +6615,21 @@
         <v>225</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>435</v>
+        <v>20</v>
       </c>
       <c r="K178" s="15">
         <v>184</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>18</v>
@@ -6638,7 +6641,7 @@
         <v>226</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>20</v>
@@ -6647,12 +6650,12 @@
         <v>184</v>
       </c>
       <c r="L179" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>18</v>
@@ -6664,7 +6667,7 @@
         <v>227</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>432</v>
+        <v>410</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>20</v>
@@ -6673,12 +6676,12 @@
         <v>184</v>
       </c>
       <c r="L180" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>18</v>
@@ -6690,21 +6693,24 @@
         <v>228</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="J181" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="K181" s="15">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L181" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>18</v>
@@ -6716,21 +6722,24 @@
         <v>229</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>20</v>
+      </c>
+      <c r="J182" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="K182" s="15">
         <v>188</v>
       </c>
       <c r="L182" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>18</v>
@@ -6742,50 +6751,41 @@
         <v>230</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J183" s="6" t="s">
-        <v>22</v>
+        <v>504</v>
       </c>
       <c r="K183" s="15">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L183" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>231</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="K184" s="15">
-        <v>190</v>
-      </c>
-      <c r="L184" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>18</v>
@@ -6796,16 +6796,22 @@
       <c r="D185" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E185" s="4" t="s">
-        <v>430</v>
+      <c r="E185" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="186" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="K185" s="15">
+        <v>192</v>
+      </c>
+      <c r="L185" s="4" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>18</v>
@@ -6816,8 +6822,8 @@
       <c r="D186" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E186" s="5" t="s">
-        <v>431</v>
+      <c r="E186" s="4" t="s">
+        <v>414</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>20</v>
@@ -6826,12 +6832,12 @@
         <v>192</v>
       </c>
       <c r="L186" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>18</v>
@@ -6843,7 +6849,7 @@
         <v>234</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>20</v>
@@ -6852,12 +6858,12 @@
         <v>192</v>
       </c>
       <c r="L187" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>18</v>
@@ -6869,7 +6875,7 @@
         <v>235</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>20</v>
@@ -6878,12 +6884,12 @@
         <v>192</v>
       </c>
       <c r="L188" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>18</v>
@@ -6895,21 +6901,24 @@
         <v>236</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="J189" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="K189" s="15">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L189" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>18</v>
@@ -6921,24 +6930,21 @@
         <v>237</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G190" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J190" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="K190" s="15">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="L190" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>18</v>
@@ -6947,24 +6953,21 @@
         <v>43</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E191" s="4" t="s">
-        <v>420</v>
+        <v>512</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>20</v>
+        <v>504</v>
       </c>
       <c r="K191" s="15">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="L191" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>18</v>
@@ -6973,18 +6976,18 @@
         <v>43</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G192" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B193" s="4" t="s">
         <v>18</v>
@@ -6993,24 +6996,24 @@
         <v>43</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G193" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K193" s="15">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L193" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B194" s="4" t="s">
         <v>18</v>
@@ -7019,27 +7022,25 @@
         <v>43</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G194" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J194" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="J194" s="6"/>
       <c r="K194" s="15">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L194" s="4" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B195" s="4" t="s">
         <v>18</v>
@@ -7048,19 +7049,19 @@
         <v>43</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="K195" s="15">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L195" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -7072,208 +7073,208 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5B0D63-9F6C-44CA-87BF-274BCE12F441}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="57" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="C1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>454</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>456</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="C3" s="10" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="C4" s="10" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>465</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>467</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>468</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>470</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="10" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>471</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>473</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D8" s="10" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>476</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>478</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D9" s="10" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>479</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>481</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>482</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>484</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D11" s="10" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>485</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>487</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="10" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>488</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>490</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
